--- a/artfynd/A 18959-2022 artfynd.xlsx
+++ b/artfynd/A 18959-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18959-2022 artfynd.xlsx
+++ b/artfynd/A 18959-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73724149</v>
+        <v>96712229</v>
       </c>
       <c r="B2" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100084</v>
+        <v>2779</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Muscardinus avellanarius</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hester, Ulricehamn, Vg</t>
+          <t>Terra inkognita, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408047.4971784087</v>
+        <v>407793</v>
       </c>
       <c r="R2" t="n">
-        <v>6407370.494170281</v>
+        <v>6407426</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-10-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-10-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Lundström</t>
+          <t>Mathias Molau</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Lundström, Morgan Johansson</t>
+          <t>Mathias Molau</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>77221979</v>
+        <v>69191391</v>
       </c>
       <c r="B3" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,19 +805,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>En route, Vg</t>
+          <t>Täppan, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>408068.6245682689</v>
+        <v>408086</v>
       </c>
       <c r="R3" t="n">
-        <v>6407406.797553021</v>
+        <v>6407343</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,22 +846,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-10-25</t>
+          <t>2017-04-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-10-25</t>
+          <t>2017-10-12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Boet gjort av gräs och björkblad. Ingen hasselmus inne i boet.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,19 +877,553 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Jeroen van der Kooij</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Pavel Bina</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Julie Dahl Møller, Alex Sattarvandi, Pavel Bina</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av hasselmus</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>73724149</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56614</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100084</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Hasselmus</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Muscardinus avellanarius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hester, Ulricehamn, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>408047</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6407370</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-10-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-10-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Magnus Lundström</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Lundström, Morgan Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>77221979</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56614</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100084</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hasselmus</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Muscardinus avellanarius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>En route, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>408069</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6407407</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2018-10-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2018-10-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
         <is>
           <t>Magnus Lundström</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Lundström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>77221980</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56614</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100084</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Hasselmus</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Muscardinus avellanarius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>En route, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>408046</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6407350</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-10-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-10-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Lundström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Lundström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>96712327</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Terra inkognita, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>407796</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6407425</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mathias Molau</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mathias Molau</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>96712328</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Terra inkognita, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>407804</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6407456</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mathias Molau</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mathias Molau</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18959-2022 artfynd.xlsx
+++ b/artfynd/A 18959-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96712229</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
           <t>Biogeografisk uppföljning av hasselmus</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69191391</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73724149</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1119,6 +1139,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77221979</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1230,6 +1255,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77221980</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1327,6 +1357,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96712327</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1424,8 +1459,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96712328</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>